--- a/data/Ficha_16_DL1153_202605_VacunaVPH.xlsx
+++ b/data/Ficha_16_DL1153_202605_VacunaVPH.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="114" r:id="rId3"/>
+    <pivotCache cacheId="125" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -94,7 +94,7 @@
     <t>PERIODO: ENERO - MAYO 2026</t>
   </si>
   <si>
-    <t>FUENTE: HISMINSA: 17/05/2026</t>
+    <t>FUENTE: HISMINSA: 24/05/2026</t>
   </si>
 </sst>
 </file>
@@ -434,7 +434,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="TuSoft" refreshedDate="46160.522675694447" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="5">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="TuSoft" refreshedDate="46167.525678935184" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="5">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabla1"/>
   </cacheSource>
@@ -465,7 +465,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="7034" maxValue="7034"/>
     </cacheField>
     <cacheField name="numerador" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="73" maxValue="374"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="73" maxValue="379"/>
     </cacheField>
     <cacheField name="Denominador1" numFmtId="0" formula="denominador/5" databaseField="0"/>
     <cacheField name="Indicador" numFmtId="0" formula="numerador/Denominador1" databaseField="0"/>
@@ -510,7 +510,7 @@
     <x v="0"/>
     <n v="9"/>
     <n v="7034"/>
-    <n v="374"/>
+    <n v="379"/>
   </r>
   <r>
     <x v="0"/>
@@ -518,13 +518,108 @@
     <x v="0"/>
     <n v="9"/>
     <n v="7034"/>
-    <n v="196"/>
+    <n v="263"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica14" cacheId="114" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica13" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+  <location ref="A8:D10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
+  <pivotFields count="8">
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+      <items count="6">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="2">
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" compact="0" outline="0" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <pageFields count="2">
+    <pageField fld="0" hier="-1"/>
+    <pageField fld="1" hier="-1"/>
+  </pageFields>
+  <dataFields count="3">
+    <dataField name="Suma de Denominador1" fld="6" baseField="0" baseItem="0"/>
+    <dataField name="Suma de numerador" fld="5" baseField="0" baseItem="0"/>
+    <dataField name="Suma de Indicador" fld="7" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <formats count="2">
+    <format dxfId="13">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="12">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleMedium13" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica14" cacheId="125" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="I8:L13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="8">
     <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
@@ -595,101 +690,6 @@
   </pageFields>
   <dataFields count="3">
     <dataField name="Suma de denominador" fld="4" baseField="0" baseItem="0"/>
-    <dataField name="Suma de numerador" fld="5" baseField="0" baseItem="0"/>
-    <dataField name="Suma de Indicador" fld="7" baseField="0" baseItem="0" numFmtId="164"/>
-  </dataFields>
-  <formats count="2">
-    <format dxfId="13">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="12">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleMedium13" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="TablaDinámica13" cacheId="114" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
-  <location ref="A8:D10" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
-  <pivotFields count="8">
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
-      <items count="6">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="2">
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" compact="0" outline="0" dragToRow="0" dragToCol="0" dragToPage="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="2"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-    <i i="2">
-      <x v="2"/>
-    </i>
-  </colItems>
-  <pageFields count="2">
-    <pageField fld="0" hier="-1"/>
-    <pageField fld="1" hier="-1"/>
-  </pageFields>
-  <dataFields count="3">
-    <dataField name="Suma de Denominador1" fld="6" baseField="0" baseItem="0"/>
     <dataField name="Suma de numerador" fld="5" baseField="0" baseItem="0"/>
     <dataField name="Suma de Indicador" fld="7" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
@@ -1125,10 +1125,10 @@
         <v>7034</v>
       </c>
       <c r="C9" s="5">
-        <v>878</v>
+        <v>950</v>
       </c>
       <c r="D9" s="6">
-        <v>0.12482229172590276</v>
+        <v>0.1350582883139039</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -1151,10 +1151,10 @@
         <v>7034</v>
       </c>
       <c r="C10" s="5">
-        <v>878</v>
+        <v>950</v>
       </c>
       <c r="D10" s="6">
-        <v>0.12482229172590276</v>
+        <v>0.1350582883139039</v>
       </c>
       <c r="I10">
         <v>2</v>
@@ -1191,10 +1191,10 @@
         <v>7034</v>
       </c>
       <c r="K12" s="5">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="L12" s="6">
-        <v>0.26585157804947401</v>
+        <v>0.26940574353141883</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -1205,10 +1205,10 @@
         <v>7034</v>
       </c>
       <c r="K13" s="5">
-        <v>196</v>
+        <v>263</v>
       </c>
       <c r="L13" s="6">
-        <v>0.13932328689223772</v>
+        <v>0.18694910435029855</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -1221,11 +1221,11 @@
       </c>
       <c r="K14" s="7">
         <f>SUM(K9:K13)</f>
-        <v>878</v>
+        <v>950</v>
       </c>
       <c r="L14" s="8">
         <f>K14/J14</f>
-        <v>0.12482229172590276</v>
+        <v>0.1350582883139039</v>
       </c>
     </row>
   </sheetData>
@@ -1345,7 +1345,7 @@
         <v>7034</v>
       </c>
       <c r="F5" s="1">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1365,7 +1365,7 @@
         <v>7034</v>
       </c>
       <c r="F6" s="1">
-        <v>196</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
